--- a/Scouting Laptop Files/ScoutingData_template.xlsx
+++ b/Scouting Laptop Files/ScoutingData_template.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\savag\OneDrive\Documents\Github\573_Lead_Scouting_App\Scouting Laptop Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A10738-E788-4110-ACFC-AA00B759D56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91959D45-58CD-4A3A-B988-0F15B280E762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="24270" windowHeight="11715" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="team_list" sheetId="3" r:id="rId2"/>
-    <sheet name="template" sheetId="2" r:id="rId3"/>
+    <sheet name="Graphs" sheetId="4" r:id="rId2"/>
+    <sheet name="team_list" sheetId="3" r:id="rId3"/>
+    <sheet name="template" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$8:$AK$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$8:$AN$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="94">
   <si>
     <t>Team Number</t>
   </si>
@@ -192,7 +193,133 @@
     <t>Defense</t>
   </si>
   <si>
-    <t>Test</t>
+    <t>Auto Total Coral Scored</t>
+  </si>
+  <si>
+    <t>Auto Total Algae Scored</t>
+  </si>
+  <si>
+    <t>TeleOp Total Coral Scored</t>
+  </si>
+  <si>
+    <t>Teleop Total Algae Scored</t>
+  </si>
+  <si>
+    <t>The Juggernauts</t>
+  </si>
+  <si>
+    <t>Team RUSH</t>
+  </si>
+  <si>
+    <t>More Martians</t>
+  </si>
+  <si>
+    <t>Adambots</t>
+  </si>
+  <si>
+    <t>Martians</t>
+  </si>
+  <si>
+    <t>The Power Chargers</t>
+  </si>
+  <si>
+    <t>The Foley Freeze</t>
+  </si>
+  <si>
+    <t>The Polar Pilots</t>
+  </si>
+  <si>
+    <t>Desperate Penguins</t>
+  </si>
+  <si>
+    <t>The Oxford RoboCats</t>
+  </si>
+  <si>
+    <t>HAZMATS</t>
+  </si>
+  <si>
+    <t>House of Cards</t>
+  </si>
+  <si>
+    <t>Kingston Robo-Cards</t>
+  </si>
+  <si>
+    <t>TESLA</t>
+  </si>
+  <si>
+    <t>Team FridgeBot</t>
+  </si>
+  <si>
+    <t>Hybrid Hornets</t>
+  </si>
+  <si>
+    <t>MarauderBots</t>
+  </si>
+  <si>
+    <t>Gears of Fortune</t>
+  </si>
+  <si>
+    <t>Owosso Robotics</t>
+  </si>
+  <si>
+    <t>Railroader Robotics</t>
+  </si>
+  <si>
+    <t>Strike Zone</t>
+  </si>
+  <si>
+    <t>Byron Robotics</t>
+  </si>
+  <si>
+    <t>Bearcats</t>
+  </si>
+  <si>
+    <t>The Underdogs</t>
+  </si>
+  <si>
+    <t>Rocket Robotics</t>
+  </si>
+  <si>
+    <t>Twin River Robotics</t>
+  </si>
+  <si>
+    <t>Cyber Soldiers</t>
+  </si>
+  <si>
+    <t>Vassar Voltage</t>
+  </si>
+  <si>
+    <t>Steel Stingers</t>
+  </si>
+  <si>
+    <t>Metal Madness</t>
+  </si>
+  <si>
+    <t>Redneck Robotics</t>
+  </si>
+  <si>
+    <t>Laker Dreadnoughts</t>
+  </si>
+  <si>
+    <t>Circuit Breakers</t>
+  </si>
+  <si>
+    <t>Bionic Bucs</t>
+  </si>
+  <si>
+    <t>Mecha Marauders</t>
+  </si>
+  <si>
+    <t>Gator Gears</t>
+  </si>
+  <si>
+    <t>Jaguar Byte</t>
+  </si>
+  <si>
+    <t>Genesee Wolves</t>
+  </si>
+  <si>
+    <t>WAY Flint</t>
   </si>
 </sst>
 </file>
@@ -252,7 +379,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -399,11 +526,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -457,10 +593,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -472,7 +606,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -487,7 +633,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1061,6 +1206,5419 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Auto Coral</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> vs Teleop Coral</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F8BE1400-E9E3-4B88-8547-4E9AD0718908}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000011-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{406AF650-1D98-41BB-8109-EFD047C2ED07}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000012-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{BE144049-AAC2-4508-9D29-6FD5AA9BA1E6}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000013-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{2D1F0D69-1595-436A-9766-18C09C0D3253}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000014-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{86811F3E-173E-4BE9-98DE-0C6B60BB82D4}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000015-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{57F64B7D-309F-42EF-8373-30E59BCF8E41}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000016-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{E7B1B394-26CC-4EDC-8C4D-B42C7A58649C}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000017-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{FF3BE4B9-61EF-408C-9837-DB7728459ED5}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000018-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{6D13F82C-2983-4C67-94FB-530D1FC688FF}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000019-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{65142C0F-9C4B-4EB1-A5CA-CCDD45E8FAEB}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001A-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{0033B631-B9A7-41DF-B2D4-837B6E6AC79B}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001B-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{0D654907-88CB-4A34-8F37-DE7897933877}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001C-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{19523508-4791-48E6-82FC-B44B324BD23D}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001D-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{496ED835-E09D-4BEE-9533-29512E5ED780}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001E-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{B66D327C-B4AB-4F97-B8A8-709273613642}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001F-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{A1B1903C-6275-4BC8-A94A-3E4BCD689D53}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000020-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="16"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{849F1B11-879F-45D1-93F1-0C3F7345FE2E}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000021-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="17"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{2919B012-14EB-4AA2-A99F-EED8F45D0854}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000022-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="18"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{5560F421-A1CB-4EBD-80DB-35A5F7097C83}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000023-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="19"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{B1DF78C0-8B0B-440E-9344-CF455D8F87DF}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000024-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="20"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{517CF7F1-CEE5-41ED-8445-E465518D8B4C}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000025-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="21"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{26B28125-D09E-4BE3-AB74-1C774288058A}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000026-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="22"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{E53F1991-6C18-4FD7-AD1B-934F85E568A4}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000027-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="23"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{32078CF3-A90E-49AD-B049-2565FC8F2E79}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000028-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="24"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{A7770017-5BB8-400B-8898-3D05E5E6B431}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000029-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="25"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{10DADB01-C18A-4114-95E7-4DE179091FAC}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002A-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="26"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{6713E01D-2DF3-49E1-A179-98EB1FB4D1E7}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002B-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="27"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{530FAD41-BE5F-4D69-AEEB-164C3BA07253}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002C-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="28"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{DFBBCE72-65E0-4E25-824A-7990EF4447F6}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002D-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="29"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{E953DC98-AED1-4754-B417-52C88042E6F1}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002E-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="30"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{614E269C-E499-431C-990E-5A1751083A11}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002F-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="31"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{BD189A0D-103F-4379-A00A-CC5FA867A3E9}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000030-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="32"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{407989B0-473D-4FBD-9424-7AB11D460D31}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000031-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="33"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{BC5D477C-5A29-4A80-A04C-7BBAFF18666B}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000032-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="34"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{0A111713-256D-45C9-9357-69C0F48E1A8C}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000033-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="35"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F55758B7-CA96-465D-99CF-DF7B5C5782BD}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000034-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="36"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{772F5082-6ECB-4042-A11F-9AAB1706A0C0}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000035-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="37"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{A04DD6B5-5EE6-422A-8735-D54D9A3B810D}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000036-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="38"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{A3D979F4-9FB6-42E5-A931-CCB1678D59A4}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000037-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="39"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{C6AD5E50-26D6-4645-94C0-FFEE83175106}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000038-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="40"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F28B9739-8D8C-4763-ACB8-9C2EA9595131}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000039-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="41"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{EB9C26DE-84B8-4EE7-AF54-7EBC72A17945}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000003A-8567-419D-B9DF-55228A7EADDC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Summary!$L$9:$L$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="42"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Summary!$B$9:$B$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="42"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>Summary!$A$9:$A$50</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="42"/>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000010-8567-419D-B9DF-55228A7EADDC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1992300543"/>
+        <c:axId val="1992301023"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1992300543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Avg</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Tele Op Coral Score</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1992301023"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1992301023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Avg</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Auto Coral Score</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1992300543"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>Teleop Algae vs. Teleop Coral</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{13A91387-9903-4A9E-8E6D-8B75A544352C}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{5E6DD5B6-5FE7-4570-AFF2-6E811D35CEC5}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{CE707A83-A8FB-47D5-B8F2-AC6B8D0C3369}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{E2C15855-4C5E-41D7-8872-2181241D731C}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{1937E850-D884-4DAC-931B-3BCAA060DC18}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{90DDF559-9F40-4C41-9150-317097EA63F2}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{4D2B5C4E-BE32-4F81-A5DD-9B992FD73A7A}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{A96DC9AA-9D84-4AF9-9A51-28C4121D7ECE}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{14A63DBF-4545-493D-BAFD-1944B52373C4}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{42645613-9CEC-4B5D-ACA8-A73B1AFD1DC7}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{6CD113CE-652B-45C3-9481-6967CEAB3A02}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{5507E093-01D1-4C0E-AA29-C8A245FE099B}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{A0761AB8-627A-4468-A204-F2D0BEC6D8E7}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{CABF4F94-4FBE-42CC-9261-ADA3DFF4E7BE}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{710C8E88-CFE9-44D8-82F8-6233C26C460A}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000E-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{396B1955-AB45-45E7-95E6-6F2F4441CD27}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000F-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="16"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{3BAED872-A5C1-4990-AA67-53EC5ECFDD34}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000010-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="17"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{2B00D497-5F9C-42DC-B6C1-76EA0B201907}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000011-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="18"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{42E3E91C-9591-40DF-A6C4-7541EB3B84BB}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000012-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="19"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{4C1666DD-3C80-45B3-B431-A38D01160223}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000013-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="20"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{32B0C566-9845-4376-888F-3958D127BA47}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000014-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="21"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{FD2F0F95-6F65-4B8B-9F7A-199732ED9279}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000015-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="22"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{75A50E83-221F-4674-A942-0420B2389726}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000016-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="23"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{92FFD1CD-0120-481D-A137-BA59A85667F0}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000017-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="24"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{309AF495-F25E-4A37-8B5D-66344D8C38D3}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000018-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="25"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{C2D40653-1771-4623-8638-1F9AE68DBED5}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000019-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="26"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{2F87C9D9-ACED-4524-9196-514A3BF18047}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001A-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="27"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{E8127628-50F6-48DF-B656-F4680781C8FE}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001B-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="28"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{068136EB-3324-4261-B759-3874181BE6FA}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001C-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="29"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{DB1DCF48-7445-46F8-9349-AD795B0678EA}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001D-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="30"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{16431851-84D7-4592-AE82-469A19D49DDF}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001E-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="31"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{C1D1CCC3-1D7C-4DF6-90AF-29BFF31B9707}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001F-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="32"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{6D1008BE-C40C-4EB1-9187-4757C86E68A4}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000020-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="33"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F3D10566-A2CC-4D6B-B8E2-934E68ABB30B}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000021-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="34"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{123E3B00-D28C-4E47-87F5-9DBAB861F040}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000022-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="35"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{5009C2CB-64B1-41B2-B3F9-F5DE75B60543}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000023-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="36"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{FEE20BC8-B675-438C-93C0-19BEE5177731}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000024-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="37"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{37B0676F-8F5D-4CF0-BAD2-1950D3872ADF}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000025-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="38"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{584356EF-E29C-4528-A1D6-7C995733CF7A}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000026-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="39"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{BAA7C6DE-2E7F-4C35-9058-4E4C26213A84}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000027-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="40"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{2BFAE14B-24C6-472D-8AEC-F25A895B8FAC}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000028-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="41"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{9CE02E93-8392-419A-8378-07DC04093772}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000029-F284-4300-AACD-8298C9C227E2}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Summary!$L$9:$L$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="42"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Summary!$M$9:$M$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="42"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>Summary!$A$9:$A$50</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="42"/>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000002A-F284-4300-AACD-8298C9C227E2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1992300543"/>
+        <c:axId val="1992301023"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1992300543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Avg</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Tele Op Coral Score</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1992301023"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1992301023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Avg</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Tele Op Algae Score</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1992300543"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B1D4897-8AC0-5A59-493D-E56C475D234E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>28574</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D78D2834-6512-4307-BE2A-C54142DFC44C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1392,442 +6950,451 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BK11"/>
+  <dimension ref="A1:BE70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="33" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="16" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="42" max="45" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="20" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="50" max="53" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="16" bestFit="1" customWidth="1"/>
-    <col min="58" max="59" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="13" customWidth="1"/>
-    <col min="63" max="63" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="37" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="44" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="20" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="52" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="13" customWidth="1"/>
+    <col min="57" max="57" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:57" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="9"/>
-    </row>
-    <row r="2" spans="1:63" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="4" spans="1:63" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:57" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="9"/>
+    </row>
+    <row r="4" spans="1:57" ht="23.25" x14ac:dyDescent="0.25">
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
-    </row>
-    <row r="5" spans="1:63" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="1:57" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
-    </row>
-    <row r="6" spans="1:63" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A6" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="25" t="s">
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:57" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A6" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="26"/>
-      <c r="R6" s="26"/>
-      <c r="S6" s="26"/>
-      <c r="T6" s="26"/>
-      <c r="U6" s="26"/>
-      <c r="V6" s="25" t="s">
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="31"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="W6" s="26"/>
-      <c r="X6" s="26"/>
-      <c r="Y6" s="26"/>
-      <c r="Z6" s="26"/>
-      <c r="AA6" s="26"/>
-      <c r="AB6" s="26"/>
-      <c r="AC6" s="26"/>
-      <c r="AD6" s="26"/>
-      <c r="AE6" s="26"/>
-      <c r="AF6" s="26"/>
-      <c r="AG6" s="26"/>
-      <c r="AH6" s="26"/>
-      <c r="AI6" s="26"/>
-      <c r="AJ6" s="26"/>
-      <c r="AK6" s="26"/>
-      <c r="AL6" s="26"/>
-      <c r="AM6" s="26"/>
-      <c r="AN6" s="26"/>
-      <c r="AO6" s="26"/>
-      <c r="AP6" s="25" t="s">
+      <c r="AA6" s="34"/>
+      <c r="AB6" s="34"/>
+      <c r="AC6" s="34"/>
+      <c r="AD6" s="34"/>
+      <c r="AE6" s="34"/>
+      <c r="AF6" s="34"/>
+      <c r="AG6" s="34"/>
+      <c r="AH6" s="34"/>
+      <c r="AI6" s="34"/>
+      <c r="AJ6" s="34"/>
+      <c r="AK6" s="34"/>
+      <c r="AL6" s="34"/>
+      <c r="AM6" s="34"/>
+      <c r="AN6" s="34"/>
+      <c r="AO6" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="AQ6" s="26"/>
-      <c r="AR6" s="26"/>
-      <c r="AS6" s="26"/>
-      <c r="AT6" s="26"/>
-      <c r="AU6" s="26"/>
-      <c r="AV6" s="26"/>
-      <c r="AW6" s="26"/>
-      <c r="AX6" s="26"/>
-      <c r="AY6" s="26"/>
-      <c r="AZ6" s="26"/>
-      <c r="BA6" s="26"/>
-      <c r="BB6" s="26"/>
-      <c r="BC6" s="26"/>
-      <c r="BD6" s="26"/>
-      <c r="BE6" s="26"/>
-      <c r="BF6" s="26"/>
-      <c r="BG6" s="26"/>
-      <c r="BH6" s="26"/>
-      <c r="BI6" s="26"/>
-      <c r="BJ6" s="22" t="s">
+      <c r="AP6" s="34"/>
+      <c r="AQ6" s="34"/>
+      <c r="AR6" s="34"/>
+      <c r="AS6" s="34"/>
+      <c r="AT6" s="34"/>
+      <c r="AU6" s="34"/>
+      <c r="AV6" s="34"/>
+      <c r="AW6" s="34"/>
+      <c r="AX6" s="34"/>
+      <c r="AY6" s="34"/>
+      <c r="AZ6" s="34"/>
+      <c r="BA6" s="34"/>
+      <c r="BB6" s="34"/>
+      <c r="BC6" s="34"/>
+      <c r="BD6" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BK6" s="19" t="s">
+      <c r="BE6" s="19" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="27" t="s">
+    <row r="7" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="27" t="s">
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
       <c r="M7" s="28"/>
       <c r="N7" s="28"/>
       <c r="O7" s="28"/>
       <c r="P7" s="28"/>
-      <c r="Q7" s="27" t="s">
-        <v>37</v>
-      </c>
+      <c r="Q7" s="28"/>
       <c r="R7" s="28"/>
       <c r="S7" s="28"/>
-      <c r="T7" s="28"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="27" t="s">
-        <v>20</v>
-      </c>
+      <c r="T7" s="29"/>
+      <c r="U7" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="V7" s="28"/>
       <c r="W7" s="28"/>
       <c r="X7" s="28"/>
-      <c r="Y7" s="28"/>
-      <c r="Z7" s="28"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="27" t="s">
+        <v>20</v>
+      </c>
       <c r="AA7" s="28"/>
       <c r="AB7" s="28"/>
-      <c r="AC7" s="29"/>
-      <c r="AD7" s="27" t="s">
-        <v>4</v>
-      </c>
+      <c r="AC7" s="28"/>
+      <c r="AD7" s="28"/>
       <c r="AE7" s="28"/>
       <c r="AF7" s="28"/>
-      <c r="AG7" s="28"/>
-      <c r="AH7" s="28"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="27" t="s">
+        <v>4</v>
+      </c>
       <c r="AI7" s="28"/>
       <c r="AJ7" s="28"/>
-      <c r="AK7" s="27" t="s">
-        <v>37</v>
-      </c>
+      <c r="AK7" s="28"/>
       <c r="AL7" s="28"/>
       <c r="AM7" s="28"/>
       <c r="AN7" s="28"/>
-      <c r="AO7" s="29"/>
-      <c r="AP7" s="27" t="s">
+      <c r="AO7" s="27" t="s">
         <v>20</v>
       </c>
+      <c r="AP7" s="28"/>
       <c r="AQ7" s="28"/>
       <c r="AR7" s="28"/>
       <c r="AS7" s="28"/>
       <c r="AT7" s="28"/>
       <c r="AU7" s="28"/>
-      <c r="AV7" s="28"/>
-      <c r="AW7" s="29"/>
-      <c r="AX7" s="27" t="s">
+      <c r="AV7" s="29"/>
+      <c r="AW7" s="27" t="s">
         <v>4</v>
       </c>
+      <c r="AX7" s="28"/>
       <c r="AY7" s="28"/>
       <c r="AZ7" s="28"/>
       <c r="BA7" s="28"/>
       <c r="BB7" s="28"/>
       <c r="BC7" s="28"/>
-      <c r="BD7" s="28"/>
-      <c r="BE7" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="BF7" s="28"/>
-      <c r="BG7" s="28"/>
-      <c r="BH7" s="28"/>
-      <c r="BI7" s="29"/>
-      <c r="BJ7" s="23" t="s">
+      <c r="BD7" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="BK7" s="20" t="s">
+      <c r="BE7" s="20" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="E8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="H8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="I8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="J8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="K8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="L8" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="O8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="P8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="Q8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="R8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="S8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="P8" s="10" t="s">
+      <c r="T8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="Q8" s="10" t="s">
+      <c r="U8" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R8" s="10" t="s">
+      <c r="V8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="S8" s="10" t="s">
+      <c r="W8" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="T8" s="10" t="s">
+      <c r="X8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="U8" s="10" t="s">
+      <c r="Y8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="V8" s="10" t="s">
+      <c r="Z8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="W8" s="10" t="s">
+      <c r="AA8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="X8" s="10" t="s">
+      <c r="AB8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="Y8" s="10" t="s">
+      <c r="AC8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="Z8" s="10" t="s">
+      <c r="AD8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AA8" s="10" t="s">
+      <c r="AE8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AB8" s="10" t="s">
+      <c r="AF8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AC8" s="10" t="s">
+      <c r="AG8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AD8" s="10" t="s">
+      <c r="AH8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="AE8" s="10" t="s">
+      <c r="AI8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="AF8" s="10" t="s">
+      <c r="AJ8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="AG8" s="10" t="s">
+      <c r="AK8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="AH8" s="10" t="s">
+      <c r="AL8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="AI8" s="10" t="s">
+      <c r="AM8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AJ8" s="10" t="s">
+      <c r="AN8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="AK8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM8" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN8" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="AO8" s="10" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AP8" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ8" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR8" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AT8" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AU8" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AV8" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AW8" s="10" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY8" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ8" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA8" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB8" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC8" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD8" s="10" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="BE8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="BF8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="BG8" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="BH8" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="BI8" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="BJ8" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="BK8" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+    <row r="9" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <f t="shared" ref="B9:B70" si="0">SUM(D9:G9)</f>
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <f>SUM(I9:J9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L69" si="1">SUM(N9:Q9)</f>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f>SUM(S9:T9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <f t="shared" ref="C10:C70" si="2">SUM(I10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f t="shared" ref="M10:M69" si="3">SUM(S10:T10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -1835,8 +7402,14 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="L11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
@@ -1853,22 +7426,1078 @@
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+    </row>
+    <row r="12" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B46">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B48">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B49">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B56">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B60">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B61">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B63">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B66">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B68">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B69">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B70">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="J7:P7"/>
-    <mergeCell ref="Q7:U7"/>
-    <mergeCell ref="B6:U6"/>
-    <mergeCell ref="V6:AO6"/>
-    <mergeCell ref="V7:AC7"/>
-    <mergeCell ref="AD7:AJ7"/>
-    <mergeCell ref="AK7:AO7"/>
-    <mergeCell ref="AP6:BI6"/>
-    <mergeCell ref="AP7:AW7"/>
-    <mergeCell ref="AX7:BD7"/>
-    <mergeCell ref="BE7:BI7"/>
+  <mergeCells count="11">
+    <mergeCell ref="Z6:AN6"/>
+    <mergeCell ref="Z7:AG7"/>
+    <mergeCell ref="AH7:AN7"/>
+    <mergeCell ref="AO6:BC6"/>
+    <mergeCell ref="AO7:AV7"/>
+    <mergeCell ref="AW7:BC7"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="U7:Y7"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="B6:Y6"/>
+    <mergeCell ref="L7:T7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
@@ -1876,8 +8505,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E8165A8-6BEB-460C-A741-C3CB92BFD262}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
@@ -1888,15 +8527,319 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>70</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>245</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>494</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>573</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B6" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>894</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>910</v>
+      </c>
+      <c r="B8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1498</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1504</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2137</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2145</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>3534</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>4994</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>4998</v>
+      </c>
+      <c r="B15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>5084</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>5150</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>5234</v>
+      </c>
+      <c r="B18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>5235</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>5260</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>5282</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>5460</v>
+      </c>
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>5641</v>
+      </c>
+      <c r="B23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>5697</v>
+      </c>
+      <c r="B24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>6067</v>
+      </c>
+      <c r="B25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>6631</v>
+      </c>
+      <c r="B26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>7195</v>
+      </c>
+      <c r="B27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>7491</v>
+      </c>
+      <c r="B28" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>7784</v>
+      </c>
+      <c r="B29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>8193</v>
+      </c>
+      <c r="B30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>8385</v>
+      </c>
+      <c r="B31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>9207</v>
+      </c>
+      <c r="B32" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>9245</v>
+      </c>
+      <c r="B33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>9648</v>
+      </c>
+      <c r="B34" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>9697</v>
+      </c>
+      <c r="B35" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>9757</v>
+      </c>
+      <c r="B36" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>9776</v>
+      </c>
+      <c r="B37" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>10659</v>
+      </c>
+      <c r="B38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>10667</v>
+      </c>
+      <c r="B39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>10668</v>
+      </c>
+      <c r="B40" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1905,7 +8848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Z20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2015,34 +8958,34 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="34" t="s">
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
+      <c r="R15" s="38"/>
+      <c r="S15" s="38"/>
       <c r="T15" s="21"/>
-      <c r="U15" s="34" t="s">
+      <c r="U15" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="V15" s="34"/>
-      <c r="W15" s="34"/>
-      <c r="X15" s="34"/>
-      <c r="Y15" s="34"/>
+      <c r="V15" s="38"/>
+      <c r="W15" s="38"/>
+      <c r="X15" s="38"/>
+      <c r="Y15" s="38"/>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
@@ -2190,9 +9133,9 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S17" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,S21:S236)</f>
-        <v/>
+      <c r="S17" s="3" t="e">
+        <f ca="1">AVERAGEIF(S21:S220,"&gt;0",S21:S200)</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3" t="e">
@@ -2283,7 +9226,10 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S18" s="3"/>
+      <c r="S18" s="3">
+        <f t="shared" ref="S18" si="5">MAX(S21:S200)</f>
+        <v>0</v>
+      </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3">
         <f t="shared" si="4"/>
@@ -2318,78 +9264,81 @@
         <v>0</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" ref="E19:O19" si="5">MIN(E21:E200)</f>
+        <f t="shared" ref="E19:O19" si="6">MIN(E21:E200)</f>
         <v>0</v>
       </c>
       <c r="F19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L19" s="4">
-        <f t="shared" ref="L19" si="6">MIN(L21:L200)</f>
+        <f t="shared" ref="L19" si="7">MIN(L21:L200)</f>
         <v>0</v>
       </c>
       <c r="M19" s="4"/>
       <c r="N19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P19" s="4">
-        <f t="shared" ref="P19:Y19" si="7">MIN(P21:P200)</f>
+        <f t="shared" ref="P19:Y19" si="8">MIN(P21:P200)</f>
         <v>0</v>
       </c>
       <c r="Q19" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R19" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="4"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="4">
+        <f t="shared" ref="S19" si="9">MIN(S21:S200)</f>
+        <v>0</v>
+      </c>
       <c r="T19" s="4"/>
       <c r="U19" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V19" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W19" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X19" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Y19" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Z19" s="24"/>
